--- a/test_membership_prices.xlsx
+++ b/test_membership_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utils\Obsidian\My Vaults\TheOracle\Yedidya-website-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{268CC939-33A9-4DE8-ADDC-06C917E2466E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83342C76-ECE6-44CA-B1CA-D5E595DF9531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15768" yWindow="192" windowWidth="14856" windowHeight="15840" xr2:uid="{34FDE9A9-4E76-44AA-80D0-FAD3860195CE}"/>
+    <workbookView xWindow="3456" yWindow="1128" windowWidth="15672" windowHeight="16152" xr2:uid="{34FDE9A9-4E76-44AA-80D0-FAD3860195CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -48,6 +48,51 @@
   </si>
   <si>
     <t>Minimum Price</t>
+  </si>
+  <si>
+    <t>תרומה כללית נוסף General Fund Additional Donation (#23683)…</t>
+  </si>
+  <si>
+    <t>מקום נוסף בעזרת נשים--אורחים וילדים בוגרים לראש השנה Additional guest and adult children seat on the women's side for Rosh Hashanah (#22979)…</t>
+  </si>
+  <si>
+    <t>מקום נוסף בעזרת נשים--אורחים וילדים בוגרים ליום כיפור Additional guest and adult children seat on the women's side for Yom Kippur (#22978)…</t>
+  </si>
+  <si>
+    <t>מקום נוסף לגברים–אורחים וילדים בוגרים ליום כיפור Additional guest and adult children seat on the men's side for Yom Kippur (#22977)…</t>
+  </si>
+  <si>
+    <t>חברי חו"ל –  יחיד\משפחה חד-הורית Overseas members – Single/Single-parent Family (#22663)…</t>
+  </si>
+  <si>
+    <t>מקום נוסף לגברים--אורחים וילדים בוגרים לראש השנה Additional guest and adult children seat on the men's side for Rosh Hashanah (#22633)…</t>
+  </si>
+  <si>
+    <t>זוג או משפחה חברי חו"ל Overseas members – couple or family (#22643)…</t>
+  </si>
+  <si>
+    <t>תרומה לקופת צדקה Tzedakah Donation (#135)…</t>
+  </si>
+  <si>
+    <t>תרומה כללית General Fund Suggested Donation (#133)…</t>
+  </si>
+  <si>
+    <t>חברים חדשים -  יחיד\משפחה חד-הורית     New members - Single/Single-parent Family (#116)…</t>
+  </si>
+  <si>
+    <t>חברים חדשים – זוג או משפחה New members – couple or family (#115)…</t>
+  </si>
+  <si>
+    <t>יחיד\משפחה חד-הורית Single/Single-parent Family (#109)…</t>
+  </si>
+  <si>
+    <t>סטודנט או חייל Student or Soldier (#108)…</t>
+  </si>
+  <si>
+    <t>חייל בודד Lone soldier (#107)…</t>
+  </si>
+  <si>
+    <t>זוג או משפחה Couple or Family Membership (#72)…</t>
   </si>
 </sst>
 </file>
@@ -83,8 +128,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,10 +465,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC5A566-ADB6-45BE-9392-1894482E5D72}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="62.77734375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,124 +482,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>23683</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>22979</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>22978</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>22977</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>22663</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>22633</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>22643</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>135</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>133</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>116</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>115</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>109</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>108</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>107</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>72</v>
       </c>
       <c r="B16">
         <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
